--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6bf74bc4b6e84ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rc1fb6a9e859649eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R8c3eb507bd054789"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R71327b22078b45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rc4b70f4a9de64d6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rf50c537654de48ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R6b283ef6473f4de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rcc6ffdbc42ab4fdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Raa5716ae928f435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R97a29a65a0624e3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R02f5128e1e3541e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R431a334ce6194bc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rda77e14ec20242c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rde214a584c6b4be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R6752792bcd604482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R99ce3f218bcd4c6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R3ee63873543f4577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R6c943191c43b44bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R7241c07809d14949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R2e1a326aea494627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R53a3e51abb4f4cfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R7a51d589565e4318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R25856e42362940df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0f82bbb2f27d4715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R845ed21b3f0049d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R2cc8eda18e1f4017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0621a6042eb846f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R4715612e11534838"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0fb0a4a5a5ca4ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5113a7bb2cdf409b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R70bae102b1854b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7ecdf795f67c4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R0aaaf6dc91b94058"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R5994327c80ca4caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc97ebb8921134f59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R58845d09dfba4777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R29f4b939263c43d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf0b0c12b686347a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R30cbd3a4f26942a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rffbfb02215024dee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R484cd508ee3e4386"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R65121cf36d8f4575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R4e44cf14fb3c4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R84b9443bc7f24736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rb6547729c9f645a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf8a5c1665c4a4a25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8915b8edc51649c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R58f02fb46b4d47cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Recd17ccada6e4534"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rae8ad2a9b2d14063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd6076f23be084487"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R83477b77f6db4b9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc665eb1889ab4e1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R6dc247f76ed64bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R99c1ee1e58c94809"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R5a534ebc94234915"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2285,11 +2285,11 @@
       </x:c>
       <x:c r="C10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" s="39" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
@@ -3678,11 +3678,11 @@
       </x:c>
       <x:c r="C37" s="41" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D37" s="41" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="41" t="n">
         <x:f>SUM(E10:E35)</x:f>
@@ -4226,7 +4226,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0c2557068e549fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc571e334ef964e2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4772,7 +4772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71e71f25f3494147"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d4e8460db94439"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5131,7 +5131,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re944c5a14b6f48bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb46aa061918a414e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5492,7 +5492,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R982fb354f1534dba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a758fbed9c454b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5851,7 +5851,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03d2a65ec3da46b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c1d1c7f63af437d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6210,7 +6210,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc785e9a1a82a4f3a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4cd34042e22448f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6534,7 +6534,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4191a949b5a460d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2ac74b8747d43b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6858,7 +6858,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7601ce49fa7a45d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R903dcd126bb84832"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7229,7 +7229,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc0886e4c5714564"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref955c5c6cb64805"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7663,7 +7663,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1c6ad09fc3b4ff8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ad1d9f3d314997"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7690,7 +7690,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="247" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -7861,7 +7861,7 @@
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="68" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>GAL-CHR-JACOB</x:v>
       </x:c>
@@ -7869,7 +7869,7 @@
         <x:v>Jacob Taylor</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -7891,7 +7891,9 @@
       </x:c>
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
-      <x:c r="L7" s="9" t="str"/>
+      <x:c r="L7" s="9" t="str">
+        <x:v>Prototype Chroniques : src/universe-actors.js, src/chronicles.js. Identifiant runtime GAL-CHR-JACOB ; contexte d’œuvre/segment et sélection de scène obligatoires.</x:v>
+      </x:c>
       <x:c r="M7" s="9" t="str"/>
       <x:c r="N7" s="9" t="str">
         <x:v>La fiche distingue identité de référence et rôle proposé.</x:v>
@@ -7907,7 +7909,7 @@
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy</x:v>
       </x:c>
       <x:c r="S7" s="20" t="str">
-        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1.</x:v>
+        <x:v>Costume exact à contrôler sur les images originales avant validation 1:1. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
@@ -7991,7 +7993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb94b846eb71485b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1cac69d7934623"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8417,7 +8419,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a664445e0f54fb2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dce37c5ddfc4565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8733,7 +8735,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621404a63e4746ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20bae8a47a1f4221"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9599,7 +9601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426ead60212f447e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde85ba6141214abc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9915,7 +9917,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf897973cf2244cd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaee45370b164efe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10268,7 +10270,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b0f8cf84b244b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411556d03d464dc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10713,7 +10715,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18ad9aae0eee4985"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb93e59ae9b1e4a74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11148,7 +11150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1011b536b3fb4d0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8750dbed11451c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11507,7 +11509,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ad306eb7694052"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fafea38ff649ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11619,12 +11621,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="40" customHeight="1">
+    <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Transformer les arènes mobiles et la narration dessinée en module ATB de poche, avec décors 3D.</x:v>
+        <x:v>Transformer les arènes mobiles et la narration dessinée en module ATB de poche, avec décors 3D. Prototype partiel : 1 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -11643,7 +11645,7 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
@@ -12093,10 +12095,16 @@
       <x:c r="E43" s="2"/>
       <x:c r="F43" s="2"/>
     </x:row>
-    <x:row r="44" ht="22" customHeight="1">
-      <x:c r="A44" s="2"/>
-      <x:c r="B44" s="2"/>
-      <x:c r="C44" s="2"/>
+    <x:row r="44" ht="96" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>Prototype Chroniques indépendant</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>1 personnages sélectionnables, 0 équipements utilisables sous restrictions d’œuvre, segment, scène et porteur ; preuves dans implementationPaths et evidence des seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>Campagne complète, dialogues, acquisition canonique, sprites, costumes, animations et statistiques originales à réaliser ou vérifier. Les ateliers sont des essais de préparation ATB, sans progression canonique ni transfert ME1.</x:v>
+      </x:c>
       <x:c r="D44" s="2"/>
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
@@ -12652,6 +12660,14 @@
       <x:c r="D113" s="2"/>
       <x:c r="E113" s="2"/>
       <x:c r="F113" s="2"/>
+    </x:row>
+    <x:row r="114" ht="22" customHeight="1">
+      <x:c r="A114" s="2"/>
+      <x:c r="B114" s="2"/>
+      <x:c r="C114" s="2"/>
+      <x:c r="D114" s="2"/>
+      <x:c r="E114" s="2"/>
+      <x:c r="F114" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13165,7 +13181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38794e8b42b3488d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c713990336a4e2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13534,7 +13550,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68ee821f95aa4183"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f631e239ff2466e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14046,7 +14062,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R256f86640cfc4142"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R533fb181f3cd4128"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14570,7 +14586,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re04ddb9102394d7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d84c059a464f8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14895,7 +14911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8762300bf1d44b21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a416c9ed594484a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15431,7 +15447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdead282dc02843fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788f8d474d554918"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15790,7 +15806,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5536f3777614c3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05f4c9d781bd4cc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0fb0a4a5a5ca4ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5113a7bb2cdf409b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R70bae102b1854b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R7ecdf795f67c4157"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R0aaaf6dc91b94058"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R5994327c80ca4caf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc97ebb8921134f59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R58845d09dfba4777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R29f4b939263c43d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf0b0c12b686347a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R30cbd3a4f26942a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rffbfb02215024dee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R484cd508ee3e4386"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R65121cf36d8f4575"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R4e44cf14fb3c4887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R84b9443bc7f24736"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rb6547729c9f645a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf8a5c1665c4a4a25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R8915b8edc51649c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R58f02fb46b4d47cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Recd17ccada6e4534"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rae8ad2a9b2d14063"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rd6076f23be084487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R83477b77f6db4b9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc665eb1889ab4e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R6dc247f76ed64bf6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R99c1ee1e58c94809"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R5a534ebc94234915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re0eb18464eba45d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9b20ce2d87bb49e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R84f98d9dbbe04290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb4c048a63c024a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R02b0bb4c94304b62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc008cd22ea0442f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4d8386d52f2d4b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3a11e416978d4f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1b854c7e9dea46de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rd04f6b3a6aad4ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2a6ebbdd500743a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R6e9058e9fd6c43bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5fb2b4bfe8cc4da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Ref9f9f0b934944fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rcc9f30f95551492e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rf9447679309b424b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R87c1fb4a797d4c5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rd48d03a48cd04e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R9bc991d079e048c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R22a12eea5c534087"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6e7d8f9a37b640bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8209e477b7c449db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re402156d82744b06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9900e794293f4fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R57390b8e5d254ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R26a6c0ca61b442bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R646c462ac38a459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rcaa444dc05954f22"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>103</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>65</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Établi")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Établi")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Établi")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$12,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$9,"Défini")</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D26" s="39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$9,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E26" s="39" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$18,"P0")</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$11,"P0")</x:f>
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$11,"P0")</x:f>
         <x:v>5</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$9,"P0")</x:f>
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>37</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>65</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>19</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4040,10 +4034,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-ENEMIES</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Category:Enemies_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4089,10 +4083,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-JATH</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Jath%27Amon</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4138,10 +4132,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-ENEMIES</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Category:Enemies_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4187,10 +4181,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>GAL-ENEMIES</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Category:Enemies_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>PV, dégâts, cadence et nombre d’unités à équilibrer pour le fan game.</x:v>
       </x:c>
     </x:row>
@@ -4226,7 +4220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc571e334ef964e2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7803f6dd06946b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4366,61 +4360,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4468,10 +4462,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4521,10 +4515,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4574,10 +4568,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4627,10 +4621,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4680,10 +4674,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4733,10 +4727,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le nombre de zones est un relevé du guide, pas un nombre de cartes 3D déjà créées.</x:v>
       </x:c>
     </x:row>
@@ -4772,7 +4766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3d4e8460db94439"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf933e805d9b248f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4912,61 +4906,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5010,8 +5004,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5053,8 +5047,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5096,8 +5090,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5131,7 +5125,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb46aa061918a414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642a817927d548cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5271,61 +5265,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5369,10 +5363,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5414,8 +5408,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5457,8 +5451,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5492,7 +5486,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77a758fbed9c454b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra51897339c144f01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5632,61 +5626,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5730,8 +5724,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5773,8 +5767,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5816,8 +5810,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -5851,7 +5845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c1d1c7f63af437d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c0bba892354661"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5991,61 +5985,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6089,8 +6083,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6132,8 +6126,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6175,8 +6169,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -6210,7 +6204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4cd34042e22448f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa119dcf4164e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6350,61 +6344,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6450,10 +6444,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-COMBAT</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Combat_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6497,10 +6491,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-ABIL</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Abilities_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -6534,7 +6528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2ac74b8747d43b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a319c170bc47e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6674,61 +6668,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6774,10 +6768,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-COMBAT</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Combat_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6821,10 +6815,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-COMBAT</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Combat_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -6858,7 +6852,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R903dcd126bb84832"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611c00d2e4c74c30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6885,7 +6879,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="250" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -6998,65 +6992,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="96" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>GAL-PWR-STASIS</x:v>
       </x:c>
@@ -7064,7 +7058,7 @@
         <x:v>Stase</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -7086,7 +7080,9 @@
       </x:c>
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
-      <x:c r="L7" s="9" t="str"/>
+      <x:c r="L7" s="9" t="str">
+        <x:v>Prototype partiel : liaison GAL-PWR-STASIS dans src/universe-powers.js, exposition par src/universe-actors.js, action native dans src/combat.js. Les acteurs, scènes et préparations autorisés sont explicitement listés par getUniversePowerUsage().</x:v>
+      </x:c>
       <x:c r="M7" s="9" t="str"/>
       <x:c r="N7" s="9" t="str">
         <x:v>La cible reprend son tour après expiration sans double action.</x:v>
@@ -7098,12 +7094,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-ABIL</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Abilities_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
-    </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v> Prototype d’action ATB : effets, coûts et durées adaptés ; arbre complet, rangs, acquisition et variantes d’édition non reproduits. Les attributions aux compagnons restent fondées sur des sources secondaires ; les classes ME2 sont recoupées avec le manuel officiel pp22–24.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="96" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>GAL-PWR-OVERLOAD</x:v>
       </x:c>
@@ -7111,7 +7109,7 @@
         <x:v>Surcharge des boucliers</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -7133,7 +7131,9 @@
       </x:c>
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
-      <x:c r="L8" s="7" t="str"/>
+      <x:c r="L8" s="7" t="str">
+        <x:v>Prototype partiel : liaison GAL-PWR-OVERLOAD dans src/universe-powers.js, exposition par src/universe-actors.js, action native dans src/combat.js. Les acteurs, scènes et préparations autorisés sont explicitement listés par getUniversePowerUsage().</x:v>
+      </x:c>
       <x:c r="M8" s="7" t="str"/>
       <x:c r="N8" s="7" t="str">
         <x:v>La barre de santé ne reçoit pas automatiquement les dégâts de bouclier.</x:v>
@@ -7145,10 +7145,12 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-ABIL</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Abilities_(Mass_Effect_Galaxy)</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str">
+        <x:v> Prototype d’action ATB : effets, coûts et durées adaptés ; arbre complet, rangs, acquisition et variantes d’édition non reproduits. Les attributions aux compagnons restent fondées sur des sources secondaires ; les classes ME2 sont recoupées avec le manuel officiel pp22–24.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7192,10 +7194,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -7229,7 +7231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref955c5c6cb64805"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4388a023153f459b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7369,61 +7371,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7475,8 +7477,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7526,8 +7528,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7577,8 +7579,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7628,8 +7630,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -7663,7 +7665,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5ad1d9f3d314997"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a0be629b3a94bc0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7803,61 +7805,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7905,10 +7907,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Costume exact à contrôler sur les images originales avant validation 1:1. Prototype partiel disponible dans les Chroniques indépendantes : profil ATB sans portrait, sprite ou moveset complet ; pouvoirs non implémentés signalés. Aucun transfert vers ME1 ni validation 1:1.</x:v>
       </x:c>
     </x:row>
@@ -7954,10 +7956,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-WIKI</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Costume exact à contrôler sur les images originales avant validation 1:1.</x:v>
       </x:c>
     </x:row>
@@ -7993,7 +7995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1cac69d7934623"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444d94ff259f433c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8133,61 +8135,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8237,8 +8239,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8286,8 +8288,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8335,8 +8337,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8384,8 +8386,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -8419,7 +8421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dce37c5ddfc4565"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb13323063ce84d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8559,61 +8561,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8657,8 +8659,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8700,8 +8702,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8735,7 +8737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20bae8a47a1f4221"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12e62c01e4574def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8875,61 +8877,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8981,8 +8983,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Le nombre de poses est une cible de production, pas une donnée du jeu source.</x:v>
       </x:c>
     </x:row>
@@ -9034,8 +9036,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Le nombre de poses est une cible de production, pas une donnée du jeu source.</x:v>
       </x:c>
     </x:row>
@@ -9087,8 +9089,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9140,8 +9142,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9193,8 +9195,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9246,8 +9248,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9299,8 +9301,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9352,8 +9354,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9405,8 +9407,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9458,8 +9460,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9511,8 +9513,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str">
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9564,8 +9566,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str">
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str">
         <x:v>Fiche de production uniquement. Aucun sprite supplémentaire n’a été généré par ce classeur.</x:v>
       </x:c>
     </x:row>
@@ -9601,7 +9603,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde85ba6141214abc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8300ebfdc5849ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9741,61 +9743,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9839,8 +9841,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9882,8 +9884,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -9917,7 +9919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaee45370b164efe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bb3b7c20b4b45a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10057,61 +10059,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10153,8 +10155,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10194,8 +10196,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10235,8 +10237,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -10270,7 +10272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R411556d03d464dc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3ba0ee35e5429e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10410,61 +10412,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10508,8 +10510,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10551,8 +10553,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10594,8 +10596,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10637,8 +10639,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10680,8 +10682,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -10715,7 +10717,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb93e59ae9b1e4a74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32d8cc6986d4cfb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10855,61 +10857,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10951,8 +10953,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10992,8 +10994,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11033,8 +11035,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11074,8 +11076,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -11115,8 +11117,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -11150,7 +11152,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8750dbed11451c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racc132686c3541be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11290,61 +11292,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11386,8 +11388,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11427,8 +11429,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11470,12 +11472,12 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-BIO, GAL-STORY, GAL-JATH</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://blog.bioware.com/2009/05/29/mass-effect-on-the-iphone/
 https://masseffect.fandom.com/wiki/Storyline_II
 https://masseffect.fandom.com/wiki/Jath%27Amon</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -11509,7 +11511,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51fafea38ff649ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e9e88ea33143b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11574,10 +11576,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -11621,12 +11623,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Transformer les arènes mobiles et la narration dessinée en module ATB de poche, avec décors 3D. Prototype partiel : 1 profils sélectionnables et 0 équipements en Chroniques ; le reste demeure documentaire.</x:v>
+        <x:v>103 fiches de production ; 3 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -11649,7 +11651,7 @@
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -11802,22 +11804,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -12026,13 +12028,13 @@
       <x:c r="F38" s="2"/>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+      <x:c r="A39" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="str">
+      <x:c r="B39" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
@@ -12109,10 +12111,16 @@
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
+    <x:row r="45" ht="96" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>2 fiches de pouvoirs utilisées, 0 familles de modules préparables et 0 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D45" s="2"/>
       <x:c r="E45" s="2"/>
       <x:c r="F45" s="2"/>
@@ -12668,6 +12676,14 @@
       <x:c r="D114" s="2"/>
       <x:c r="E114" s="2"/>
       <x:c r="F114" s="2"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="2"/>
+      <x:c r="B115" s="2"/>
+      <x:c r="C115" s="2"/>
+      <x:c r="D115" s="2"/>
+      <x:c r="E115" s="2"/>
+      <x:c r="F115" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12809,61 +12825,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12909,10 +12925,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-WIKI</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12956,10 +12972,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13003,10 +13019,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13050,10 +13066,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13097,10 +13113,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13144,10 +13160,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>GAL-TUDGE</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Reginald_Tudge</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -13181,7 +13197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c713990336a4e2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca5ce1174ea4aac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13321,61 +13337,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13419,10 +13435,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-BIO</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2009/05/29/mass-effect-on-the-iphone/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13466,10 +13482,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13513,10 +13529,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-STORY</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_II</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -13550,7 +13566,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f631e239ff2466e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69faec4f8a894844"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13690,61 +13706,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13790,10 +13806,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13837,10 +13853,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13884,10 +13900,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13931,10 +13947,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13978,10 +13994,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14025,10 +14041,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -14062,7 +14078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R533fb181f3cd4128"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82edddbfec2481e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14202,61 +14218,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14306,8 +14322,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14355,8 +14371,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -14404,8 +14420,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -14453,8 +14469,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -14502,8 +14518,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -14551,8 +14567,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -14586,7 +14602,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d84c059a464f8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7124f208e8604a03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14726,61 +14742,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14826,11 +14842,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>GAL-BIO, GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://blog.bioware.com/2009/05/29/mass-effect-on-the-iphone/
 https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -14874,10 +14890,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>GAL-GUIDE</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Mass_Effect_Galaxy_Guide</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -14911,7 +14927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a416c9ed594484a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88b4a9efb5334786"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15051,61 +15067,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15157,8 +15173,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15208,8 +15224,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15259,8 +15275,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -15310,8 +15326,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -15361,8 +15377,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -15412,8 +15428,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -15447,7 +15463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788f8d474d554918"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8563557a5db84199"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15587,61 +15603,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15685,8 +15701,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="44" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15728,8 +15744,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15771,8 +15787,8 @@
         <x:v>Conception du fan game</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D9">
@@ -15806,7 +15822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05f4c9d781bd4cc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec503b10ee1e4022"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re0eb18464eba45d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R9b20ce2d87bb49e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R84f98d9dbbe04290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rb4c048a63c024a02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R02b0bb4c94304b62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rc008cd22ea0442f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R4d8386d52f2d4b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3a11e416978d4f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1b854c7e9dea46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rd04f6b3a6aad4ea2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2a6ebbdd500743a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R6e9058e9fd6c43bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R5fb2b4bfe8cc4da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Ref9f9f0b934944fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rcc9f30f95551492e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rf9447679309b424b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R87c1fb4a797d4c5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rd48d03a48cd04e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R9bc991d079e048c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R22a12eea5c534087"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R6e7d8f9a37b640bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R8209e477b7c449db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Re402156d82744b06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9900e794293f4fd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R57390b8e5d254ed8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R26a6c0ca61b442bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R646c462ac38a459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rcaa444dc05954f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7d52ff6dfebf4eed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R96ffa4c003dc4276"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R89d78e5904ed4c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R96309e431a6e4ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rd9357f2273084d68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R27b243c6e1354541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R906bd3591d48466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ra93d82853a5e4b40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re912ca51ec224773"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8556ebbd49e74341"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7ace9eb29b484da1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2b190bfb27104f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3360b417deba4d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2b9c05331c8849e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R4f111adbe1a54ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rc40b8c77946f40e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R52175c25d23c4ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rfe772cd2a93e46b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R22d978ddfd2c4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rea571c9637104dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R10ff9f3155af44d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R27669470076547fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfea805ede26a4ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb057c06896da45c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc2118158a83548bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Red9e42b0c8224579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1dbd4ea91c5648d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R540211b4f02d481c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4220,7 +4220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7803f6dd06946b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea6540ccc7884226"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4766,7 +4766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf933e805d9b248f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R417295664faf4539"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5125,7 +5125,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R642a817927d548cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72efeec81c334469"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5486,7 +5486,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra51897339c144f01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd630c5a803344c50"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5845,7 +5845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50c0bba892354661"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413fe59eacbe4609"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6204,7 +6204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fa119dcf4164e3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05be078b426441b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6528,7 +6528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04a319c170bc47e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79b4c88aa6343e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6852,7 +6852,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611c00d2e4c74c30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R877296bf0da5432c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7231,7 +7231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4388a023153f459b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra151a564d8ae4cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a0be629b3a94bc0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad9093213c7f4a92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7995,7 +7995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R444d94ff259f433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7bad878d2e4b03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8421,7 +8421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb13323063ce84d3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdbc45e6a7f43c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8737,7 +8737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12e62c01e4574def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ec408f5a6343b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9603,7 +9603,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8300ebfdc5849ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd1e8ae1df574465"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9919,7 +9919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5bb3b7c20b4b45a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra203db48c4fe44c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10272,7 +10272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a3ba0ee35e5429e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d850115003a4824"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10717,7 +10717,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd32d8cc6986d4cfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R446d479664d54991"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11152,7 +11152,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racc132686c3541be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e994b5a5faf45f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11511,7 +11511,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0e9e88ea33143b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7427bd6cd7e40c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13197,7 +13197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca5ce1174ea4aac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63bcf801cfbb4f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13566,7 +13566,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69faec4f8a894844"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62e3c73c96a14f2b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14078,7 +14078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb82edddbfec2481e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79afe0f204f34fb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14602,7 +14602,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7124f208e8604a03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec140cc23fa4ce0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14927,7 +14927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88b4a9efb5334786"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8abb64f4067a4d1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15463,7 +15463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8563557a5db84199"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaabafc4378546ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15822,7 +15822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec503b10ee1e4022"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f60966deb34887"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7d52ff6dfebf4eed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R96ffa4c003dc4276"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R89d78e5904ed4c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R96309e431a6e4ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rd9357f2273084d68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R27b243c6e1354541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R906bd3591d48466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Ra93d82853a5e4b40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re912ca51ec224773"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R8556ebbd49e74341"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7ace9eb29b484da1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R2b190bfb27104f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R3360b417deba4d01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R2b9c05331c8849e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R4f111adbe1a54ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Rc40b8c77946f40e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R52175c25d23c4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rfe772cd2a93e46b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R22d978ddfd2c4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rea571c9637104dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R10ff9f3155af44d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R27669470076547fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfea805ede26a4ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rb057c06896da45c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rc2118158a83548bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Red9e42b0c8224579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R1dbd4ea91c5648d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R540211b4f02d481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R58ea2a5a689d4af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rbbfa5d0d5315459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R7e8c2329f92341b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rdcbb7ce1aadf4ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R20eb993bac784ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcfaacb3165ca4f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re4141cc6c94c44c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R72846a5f2ca14ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Reb2c00a0179e4036"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R510261636b6a43f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2af5abf8ba8c4759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R487dd583e9b6448d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R743fb50984f3445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb35e58cc155b459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8307e41d618448e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9aba4e0dc1c04c37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rd7bea65f1a2f4dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re3764d26d3674bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R32fd39eef85145f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R18094256fcd04220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra49137e199ce4519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf200b4f0f8c6407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R27200bf4354a4166"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0a682f6f62204870"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R37cd0ed46dca42f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0f254a0c53a84c75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0d71abd821c64830"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb2ab462f0f2c4655"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4220,7 +4220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea6540ccc7884226"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R643ccd8f70634f0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4766,7 +4766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R417295664faf4539"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5da5516d476492c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5125,7 +5125,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R72efeec81c334469"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1320b009877b4f3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5486,7 +5486,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd630c5a803344c50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74122b9decfd470a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5845,7 +5845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R413fe59eacbe4609"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c6bb025f944a6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6204,7 +6204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05be078b426441b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1453b6f91d4a17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6528,7 +6528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf79b4c88aa6343e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11017b5d8ff04774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6852,7 +6852,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R877296bf0da5432c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40058e84a0814d01"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7231,7 +7231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra151a564d8ae4cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78256c16a04c4c39"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad9093213c7f4a92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7de43f30c24843"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7995,7 +7995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e7bad878d2e4b03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fbb9745b17f470a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8421,7 +8421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdbc45e6a7f43c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red10da2b0ec4458e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8737,7 +8737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92ec408f5a6343b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ccacd99d7b49c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9603,7 +9603,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd1e8ae1df574465"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9df087b4e847f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9919,7 +9919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra203db48c4fe44c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26e0d0d216d4444e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10272,7 +10272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d850115003a4824"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3013059e9e344a0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10717,7 +10717,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R446d479664d54991"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac83d49c63e4791"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11152,7 +11152,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e994b5a5faf45f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d2cb7093a7b4aee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11511,7 +11511,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7427bd6cd7e40c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc43b77fb25224435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13197,7 +13197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63bcf801cfbb4f9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radda13bd66034884"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13566,7 +13566,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62e3c73c96a14f2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raba4bdfa00784830"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14078,7 +14078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79afe0f204f34fb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc922e30b37848b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14602,7 +14602,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec140cc23fa4ce0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea5d8d532a99479a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14927,7 +14927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8abb64f4067a4d1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8c38b01cb8f4ed6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15463,7 +15463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaabafc4378546ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ae0535f5da4c6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15822,7 +15822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8f60966deb34887"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd828a8da556c48bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Galaxy_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R58ea2a5a689d4af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rbbfa5d0d5315459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R7e8c2329f92341b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rdcbb7ce1aadf4ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R20eb993bac784ae2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcfaacb3165ca4f10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re4141cc6c94c44c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R72846a5f2ca14ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Reb2c00a0179e4036"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R510261636b6a43f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R2af5abf8ba8c4759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R487dd583e9b6448d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R743fb50984f3445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb35e58cc155b459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R8307e41d618448e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9aba4e0dc1c04c37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rd7bea65f1a2f4dd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re3764d26d3674bdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R32fd39eef85145f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R18094256fcd04220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra49137e199ce4519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rf200b4f0f8c6407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R27200bf4354a4166"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0a682f6f62204870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R37cd0ed46dca42f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R0f254a0c53a84c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R0d71abd821c64830"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb2ab462f0f2c4655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R8039fb6a36854034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R690d42bb13e14197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R92f2446f48cb44b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd1e5ce61a028471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R894a70a80e354d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R98154d95efd94837"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R04366753e21347a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R273a810309f24d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rec6add4e1a794304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rf21ac7447fd2483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R50ec4b5e40794164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R6b4208769cd94b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rf2651f2213ca4bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R3f6f772e89fe457e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Ra178072c5abc420b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Reb6565d043c54c66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R6ea1893e5c3b4412"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf48f5719246d402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rc6135ff7c144470a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R603c9a836e0b48aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R094aab850d3845d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rca89f9a0b90e4926"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R46e927cc5f0447b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R0ae6e3ca72154eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rf5dd304a79644319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf8ebef8aa5864fa5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rffa67f8e0e224e94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R7f2522ca692c4210"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4220,7 +4220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R643ccd8f70634f0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06977e4b92274a6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4766,7 +4766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5da5516d476492c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0751d767c9864b1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5125,7 +5125,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1320b009877b4f3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71dc197c8f844882"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5486,7 +5486,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74122b9decfd470a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e8b4f07c5d4410f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5845,7 +5845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c6bb025f944a6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc6ae37990ba461d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6204,7 +6204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b1453b6f91d4a17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra525b4fac50242ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6528,7 +6528,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11017b5d8ff04774"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08d473553d6844ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6852,7 +6852,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40058e84a0814d01"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c17ec1117194e97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7231,7 +7231,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78256c16a04c4c39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9db1dbf34a394e4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7665,7 +7665,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7de43f30c24843"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cd648c4b49d406c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7995,7 +7995,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fbb9745b17f470a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0db6396e5404979"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8421,7 +8421,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red10da2b0ec4458e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dcbb679a9a04b15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8737,7 +8737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ccacd99d7b49c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4b6e30d30da475d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9603,7 +9603,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref9df087b4e847f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce770c920cc24fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9919,7 +9919,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26e0d0d216d4444e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdafc04e9cfd44feb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10272,7 +10272,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3013059e9e344a0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39ade1c8b4ff4b88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10717,7 +10717,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac83d49c63e4791"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8696e0d52714097"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11152,7 +11152,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d2cb7093a7b4aee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec06f2f830514dda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11511,7 +11511,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc43b77fb25224435"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8db5fdef8b2b4006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13197,7 +13197,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radda13bd66034884"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47129fb390ec4699"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13566,7 +13566,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raba4bdfa00784830"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd6aa2a6673844a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14078,7 +14078,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc922e30b37848b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8927b05fe2d740fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14602,7 +14602,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea5d8d532a99479a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5202400351a4dbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14927,7 +14927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8c38b01cb8f4ed6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15a129bec10c4741"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15463,7 +15463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ae0535f5da4c6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc498a653b53947b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15822,7 +15822,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd828a8da556c48bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fcfc2b102d43ad"/>
   </x:tableParts>
 </x:worksheet>
 </file>